--- a/data/csv/Healthcare.xlsx
+++ b/data/csv/Healthcare.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wfpin\Desktop\Projects\gravity\data\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABAF2B17-CADF-417B-BCFF-CAB50C07035A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9200381-1867-4A50-BF00-CD4B84525EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{E6FF7B8D-42F5-4752-AA26-910C7E84BE64}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>A</t>
   </si>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>HCA</t>
-  </si>
-  <si>
-    <t>HOLX</t>
   </si>
   <si>
     <t>HSIC</t>
@@ -590,12 +587,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E0E734-BFE6-4A84-A9EF-FCC6065472EB}">
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -891,11 +888,6 @@
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
